--- a/game22/web.xlsx
+++ b/game22/web.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>domain</t>
   </si>
@@ -46,37 +46,49 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.vernations.cloud</t>
+    <t>play.ostensory.cloud</t>
+  </si>
+  <si>
+    <t>#98fb98</t>
+  </si>
+  <si>
+    <t>sec.ostensory.cloud</t>
+  </si>
+  <si>
+    <t>play.narthex.cloud</t>
+  </si>
+  <si>
+    <t>#ba55d3</t>
+  </si>
+  <si>
+    <t>sec.narthex.cloud</t>
+  </si>
+  <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>orrerys.top</t>
   </si>
   <si>
     <t>#ffa500</t>
   </si>
   <si>
-    <t>play.mizars.cloud</t>
+    <t>armillary.top</t>
   </si>
   <si>
     <t>#9d4edd</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>orrerys.top</t>
-  </si>
-  <si>
-    <t>armillary.top</t>
   </si>
   <si>
     <t>theodolite.top</t>
@@ -134,7 +146,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -167,14 +179,6 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -338,7 +342,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="47">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,6 +429,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF98FB98"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA55D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF70C588"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -616,25 +632,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -738,85 +741,79 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -825,10 +822,10 @@
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -837,10 +834,10 @@
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -849,10 +846,10 @@
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -861,10 +858,10 @@
     <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -873,17 +870,23 @@
     <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -933,16 +936,19 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1369,8 +1375,8 @@
       <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>8</v>
+      <c r="B3" s="18" t="s">
+        <v>6</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1380,39 +1386,61 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1"/>
       <c r="B6" s="16"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="19" t="s">
-        <v>9</v>
+      <c r="F16" s="20" t="s">
+        <v>11</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="6:7">
-      <c r="F17" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>12</v>
+      <c r="F17" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
     <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
-    <hyperlink ref="A2" r:id="rId3" display="play.vernations.cloud"/>
-    <hyperlink ref="A3" r:id="rId4" display="play.mizars.cloud"/>
+    <hyperlink ref="A2" r:id="rId3" display="play.ostensory.cloud"/>
+    <hyperlink ref="A3" r:id="rId3" display="sec.ostensory.cloud"/>
+    <hyperlink ref="A4" r:id="rId4" display="play.narthex.cloud"/>
+    <hyperlink ref="A5" r:id="rId4" display="sec.narthex.cloud"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1430,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1444,10 +1472,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1458,10 +1486,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1472,10 +1500,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1486,10 +1514,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1500,10 +1528,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1532,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1540,49 +1568,49 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
